--- a/시흥캠퍼스_식당카페_조사템플릿.xlsx
+++ b/시흥캠퍼스_식당카페_조사템플릿.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="general"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,7 +131,59 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="008C1D18"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="008E1B4B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="005B2A6B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00283593"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <color rgb="008A4B08"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="008A4B08"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="008C2F14"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="004E342E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="0037474F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="007A6100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00556B00"/>
       <sz val="10"/>
     </font>
     <font>
@@ -148,6 +200,11 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00B3261E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
@@ -246,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -268,11 +325,25 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="medium">
+        <color rgb="007A7A7A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -335,73 +406,224 @@
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="16" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="28" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -410,7 +632,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7651,7 +7873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7748,7 +7970,7 @@
       </c>
       <c r="B2" s="23" t="inlineStr">
         <is>
-          <t>배곧할매순대국 배곧본점</t>
+          <t>배곧한상 배곧본점</t>
         </is>
       </c>
       <c r="C2" s="22" t="inlineStr">
@@ -7778,7 +8000,7 @@
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
-          <t>031-000-0000</t>
+          <t>031-000-0001</t>
         </is>
       </c>
       <c r="I2" s="24" t="n">
@@ -7803,429 +8025,863 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="22" t="n">
+      <c r="A3" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>배곧할매순대국 배곧본점</t>
-        </is>
-      </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>배곧한상 배곧본점</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>식당</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>한식</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>경기 시흥시 배곧4로 00, 1층</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>10:00~22:00 (브레이크타임 15:00~16:30)</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>매주 월요일</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
-        <is>
-          <t>031-000-0000</t>
-        </is>
-      </c>
-      <c r="I3" s="24" t="n">
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>031-000-0001</t>
+        </is>
+      </c>
+      <c r="I3" s="29" t="n">
         <v>4.6</v>
       </c>
-      <c r="J3" s="25" t="n">
+      <c r="J3" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="K3" s="26" t="n">
+      <c r="K3" s="31" t="n">
         <v>12000</v>
       </c>
-      <c r="L3" s="25" t="n">
+      <c r="L3" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="23" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t>모둠순대</t>
         </is>
       </c>
-      <c r="N3" s="26" t="n">
+      <c r="N3" s="31" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="22" t="n">
+      <c r="A4" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>배곧할매순대국 배곧본점</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>배곧한상 배곧본점</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>식당</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>한식</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>경기 시흥시 배곧4로 00, 1층</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>10:00~22:00 (브레이크타임 15:00~16:30)</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>매주 월요일</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t>031-000-0000</t>
-        </is>
-      </c>
-      <c r="I4" s="24" t="n">
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>031-000-0001</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="n">
         <v>4.6</v>
       </c>
-      <c r="J4" s="25" t="n">
+      <c r="J4" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="K4" s="26" t="n">
+      <c r="K4" s="31" t="n">
         <v>12000</v>
       </c>
-      <c r="L4" s="25" t="n">
+      <c r="L4" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="23" t="inlineStr">
-        <is>
-          <t>돼지국밥</t>
-        </is>
-      </c>
-      <c r="N4" s="26" t="n">
+      <c r="M4" s="28" t="inlineStr">
+        <is>
+          <t>제육볶음</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>교촌치킨 시흥배곧점</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>배곧반점 배곧중앙점</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>식당</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>중식</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧중앙로 00</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
+        <is>
+          <t>11:00~21:30</t>
+        </is>
+      </c>
+      <c r="G5" s="33" t="inlineStr">
+        <is>
+          <t>매주 화요일</t>
+        </is>
+      </c>
+      <c r="H5" s="33" t="inlineStr">
+        <is>
+          <t>031-000-0002</t>
+        </is>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="33" t="inlineStr">
+        <is>
+          <t>짜장면</t>
+        </is>
+      </c>
+      <c r="N5" s="36" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>스시배곧 배곧해솔점</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>일식</t>
+        </is>
+      </c>
+      <c r="E6" s="38" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧해솔로 00, 2층</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="inlineStr">
+        <is>
+          <t>11:30~21:00 (브레이크타임 15:00~17:00)</t>
+        </is>
+      </c>
+      <c r="G6" s="38" t="inlineStr">
+        <is>
+          <t>매주 월요일</t>
+        </is>
+      </c>
+      <c r="H6" s="38" t="inlineStr">
+        <is>
+          <t>031-000-0003</t>
+        </is>
+      </c>
+      <c r="I6" s="39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" s="40" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="41" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="38" t="inlineStr">
+        <is>
+          <t>모둠초밥 10P</t>
+        </is>
+      </c>
+      <c r="N6" s="41" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>파스타공방 배곧점</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>양식</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧2로 00</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>11:00~22:00</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>연중무휴</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>031-000-0004</t>
+        </is>
+      </c>
+      <c r="I7" s="44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="K7" s="46" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L7" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="43" t="inlineStr">
+        <is>
+          <t>크림파스타</t>
+        </is>
+      </c>
+      <c r="N7" s="46" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>바삭치킨 시흥배곧점</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>치킨</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧3로 00</t>
+        </is>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>15:00~01:00</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="inlineStr">
+        <is>
+          <t>연중무휴</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="inlineStr">
+        <is>
+          <t>031-000-0005</t>
+        </is>
+      </c>
+      <c r="I8" s="49" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="K8" s="51" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L8" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="48" t="inlineStr">
+        <is>
+          <t>후라이드 한마리</t>
+        </is>
+      </c>
+      <c r="N8" s="51" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>바삭치킨 시흥배곧점</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>치킨</t>
+        </is>
+      </c>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧3로 00</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>15:00~01:00</t>
+        </is>
+      </c>
+      <c r="G9" s="53" t="inlineStr">
+        <is>
+          <t>연중무휴</t>
+        </is>
+      </c>
+      <c r="H9" s="53" t="inlineStr">
+        <is>
+          <t>031-000-0005</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" s="55" t="n">
+        <v>45</v>
+      </c>
+      <c r="K9" s="56" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L9" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="53" t="inlineStr">
+        <is>
+          <t>양념 한마리</t>
+        </is>
+      </c>
+      <c r="N9" s="56" t="n">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>오븐피자 배곧한라점</t>
+        </is>
+      </c>
+      <c r="C10" s="57" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>피자</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧해솔로 00, 1층</t>
+        </is>
+      </c>
+      <c r="F10" s="58" t="inlineStr">
+        <is>
+          <t>11:00~23:00</t>
+        </is>
+      </c>
+      <c r="G10" s="58" t="inlineStr">
+        <is>
+          <t>연중무휴</t>
+        </is>
+      </c>
+      <c r="H10" s="58" t="inlineStr">
+        <is>
+          <t>031-000-0006</t>
+        </is>
+      </c>
+      <c r="I10" s="59" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="61" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L10" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t>페퍼로니피자(L)</t>
+        </is>
+      </c>
+      <c r="N10" s="61" t="n">
+        <v>24900</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>배곧왕족발 본점</t>
+        </is>
+      </c>
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D11" s="62" t="inlineStr">
+        <is>
+          <t>족발</t>
+        </is>
+      </c>
+      <c r="E11" s="63" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧4로 00</t>
+        </is>
+      </c>
+      <c r="F11" s="63" t="inlineStr">
+        <is>
+          <t>16:00~02:00</t>
+        </is>
+      </c>
+      <c r="G11" s="63" t="inlineStr">
+        <is>
+          <t>매주 일요일</t>
+        </is>
+      </c>
+      <c r="H11" s="63" t="inlineStr">
+        <is>
+          <t>031-000-0007</t>
+        </is>
+      </c>
+      <c r="I11" s="64" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" s="65" t="n">
+        <v>50</v>
+      </c>
+      <c r="K11" s="66" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L11" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="63" t="inlineStr">
+        <is>
+          <t>족발(중)</t>
+        </is>
+      </c>
+      <c r="N11" s="66" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="68" t="inlineStr">
+        <is>
+          <t>참보쌈 배곧사거리점</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D12" s="67" t="inlineStr">
+        <is>
+          <t>보쌈</t>
+        </is>
+      </c>
+      <c r="E12" s="68" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧중앙로 00, 1층</t>
+        </is>
+      </c>
+      <c r="F12" s="68" t="inlineStr">
+        <is>
+          <t>16:00~24:00</t>
+        </is>
+      </c>
+      <c r="G12" s="68" t="inlineStr">
+        <is>
+          <t>매주 월요일</t>
+        </is>
+      </c>
+      <c r="H12" s="68" t="inlineStr">
+        <is>
+          <t>031-000-0008</t>
+        </is>
+      </c>
+      <c r="I12" s="69" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" s="70" t="n">
+        <v>45</v>
+      </c>
+      <c r="K12" s="71" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L12" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="68" t="inlineStr">
+        <is>
+          <t>보쌈정식(2인)</t>
+        </is>
+      </c>
+      <c r="N12" s="71" t="n">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="72" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="73" t="inlineStr">
+        <is>
+          <t>배곧떡볶이 배곧점</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D13" s="72" t="inlineStr">
+        <is>
+          <t>분식</t>
+        </is>
+      </c>
+      <c r="E13" s="73" t="inlineStr">
         <is>
           <t>경기 시흥시 배곧2로 00</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>15:00~01:00</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="F13" s="73" t="inlineStr">
+        <is>
+          <t>11:00~21:00</t>
+        </is>
+      </c>
+      <c r="G13" s="73" t="inlineStr">
+        <is>
+          <t>매주 일요일</t>
+        </is>
+      </c>
+      <c r="H13" s="73" t="inlineStr">
+        <is>
+          <t>031-000-0009</t>
+        </is>
+      </c>
+      <c r="I13" s="74" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J13" s="75" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="76" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L13" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="73" t="inlineStr">
+        <is>
+          <t>국물떡볶이</t>
+        </is>
+      </c>
+      <c r="N13" s="76" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="78" t="inlineStr">
+        <is>
+          <t>버거하우스 시흥배곧점</t>
+        </is>
+      </c>
+      <c r="C14" s="77" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D14" s="77" t="inlineStr">
+        <is>
+          <t>패스트푸드</t>
+        </is>
+      </c>
+      <c r="E14" s="78" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧중앙로 00</t>
+        </is>
+      </c>
+      <c r="F14" s="78" t="inlineStr">
+        <is>
+          <t>10:00~24:00</t>
+        </is>
+      </c>
+      <c r="G14" s="78" t="inlineStr">
         <is>
           <t>연중무휴</t>
         </is>
       </c>
-      <c r="H5" s="28" t="inlineStr">
-        <is>
-          <t>031-000-0001</t>
-        </is>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J5" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="K5" s="31" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L5" s="30" t="n">
+      <c r="H14" s="78" t="inlineStr">
+        <is>
+          <t>031-000-0010</t>
+        </is>
+      </c>
+      <c r="I14" s="79" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J14" s="80" t="n">
+        <v>30</v>
+      </c>
+      <c r="K14" s="81" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L14" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="28" t="inlineStr">
-        <is>
-          <t>허니콤보</t>
-        </is>
-      </c>
-      <c r="N5" s="31" t="n">
-        <v>23000</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>교촌치킨 시흥배곧점</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>식당</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>치킨</t>
-        </is>
-      </c>
-      <c r="E6" s="28" t="inlineStr">
-        <is>
-          <t>경기 시흥시 배곧2로 00</t>
-        </is>
-      </c>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>15:00~01:00</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="M14" s="78" t="inlineStr">
+        <is>
+          <t>치즈버거 세트</t>
+        </is>
+      </c>
+      <c r="N14" s="81" t="n">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="82" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>배곧커피 배곧한라비발디점</t>
+        </is>
+      </c>
+      <c r="C15" s="82" t="inlineStr">
+        <is>
+          <t>카페</t>
+        </is>
+      </c>
+      <c r="D15" s="82" t="inlineStr">
+        <is>
+          <t>카페</t>
+        </is>
+      </c>
+      <c r="E15" s="83" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧해솔로 00</t>
+        </is>
+      </c>
+      <c r="F15" s="83" t="inlineStr">
+        <is>
+          <t>07:00~23:00</t>
+        </is>
+      </c>
+      <c r="G15" s="83" t="inlineStr">
         <is>
           <t>연중무휴</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
-        <is>
-          <t>031-000-0001</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J6" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="K6" s="31" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L6" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="28" t="inlineStr">
-        <is>
-          <t>레드윙</t>
-        </is>
-      </c>
-      <c r="N6" s="31" t="n">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>메가MGC커피 배곧한라비발디점</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="H15" s="83" t="inlineStr">
+        <is>
+          <t>031-000-0011</t>
+        </is>
+      </c>
+      <c r="I15" s="84" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" s="85" t="n">
+        <v>25</v>
+      </c>
+      <c r="K15" s="86" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L15" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="83" t="inlineStr">
+        <is>
+          <t>아메리카노(ICE)</t>
+        </is>
+      </c>
+      <c r="N15" s="86" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="87" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="88" t="inlineStr">
+        <is>
+          <t>눈꽃빙수 배곧점</t>
+        </is>
+      </c>
+      <c r="C16" s="87" t="inlineStr">
         <is>
           <t>카페</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>카페</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>경기 시흥시 배곧해솔로 00</t>
-        </is>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>07:00~23:00</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>연중무휴</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>031-000-0002</t>
-        </is>
-      </c>
-      <c r="I7" s="34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J7" s="35" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" s="36" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L7" s="35" t="n">
+      <c r="D16" s="87" t="inlineStr">
+        <is>
+          <t>디저트</t>
+        </is>
+      </c>
+      <c r="E16" s="88" t="inlineStr">
+        <is>
+          <t>경기 시흥시 배곧중앙로 00, 2층</t>
+        </is>
+      </c>
+      <c r="F16" s="88" t="inlineStr">
+        <is>
+          <t>11:00~22:00</t>
+        </is>
+      </c>
+      <c r="G16" s="88" t="inlineStr">
+        <is>
+          <t>설·추석 당일</t>
+        </is>
+      </c>
+      <c r="H16" s="88" t="inlineStr">
+        <is>
+          <t>031-000-0012</t>
+        </is>
+      </c>
+      <c r="I16" s="89" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J16" s="90" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" s="91" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L16" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="33" t="inlineStr">
-        <is>
-          <t>아메리카노(ICE)</t>
-        </is>
-      </c>
-      <c r="N7" s="36" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>메가MGC커피 배곧한라비발디점</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>카페</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>카페</t>
-        </is>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t>경기 시흥시 배곧해솔로 00</t>
-        </is>
-      </c>
-      <c r="F8" s="33" t="inlineStr">
-        <is>
-          <t>07:00~23:00</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>연중무휴</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>031-000-0002</t>
-        </is>
-      </c>
-      <c r="I8" s="34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" s="35" t="n">
-        <v>25</v>
-      </c>
-      <c r="K8" s="36" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L8" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="33" t="inlineStr">
-        <is>
-          <t>카페라떼(ICE)</t>
-        </is>
-      </c>
-      <c r="N8" s="36" t="n">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="38" t="inlineStr">
-        <is>
-          <t>설빙 배곧점</t>
-        </is>
-      </c>
-      <c r="C9" s="37" t="inlineStr">
-        <is>
-          <t>카페</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="inlineStr">
-        <is>
-          <t>디저트</t>
-        </is>
-      </c>
-      <c r="E9" s="38" t="inlineStr">
-        <is>
-          <t>경기 시흥시 배곧중앙로 00, 2층</t>
-        </is>
-      </c>
-      <c r="F9" s="38" t="inlineStr">
-        <is>
-          <t>11:00~22:00</t>
-        </is>
-      </c>
-      <c r="G9" s="38" t="inlineStr">
-        <is>
-          <t>설·추석 당일</t>
-        </is>
-      </c>
-      <c r="H9" s="38" t="inlineStr">
-        <is>
-          <t>031-000-0003</t>
-        </is>
-      </c>
-      <c r="I9" s="39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J9" s="40" t="n">
-        <v>40</v>
-      </c>
-      <c r="K9" s="41" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L9" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="38" t="inlineStr">
-        <is>
-          <t>인절미설빙</t>
-        </is>
-      </c>
-      <c r="N9" s="41" t="n">
+      <c r="M16" s="88" t="inlineStr">
+        <is>
+          <t>인절미빙수</t>
+        </is>
+      </c>
+      <c r="N16" s="91" t="n">
         <v>9900</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>※ 대표메뉴가 여러 개인 매장은 매장 정보를 그대로 반복해서 쓰고, 메뉴순번만 1·2·3으로 올려가며 행을 추가합니다. 매장번호가 같으면 같은 매장으로 봅니다.</t>
+    <row r="18">
+      <c r="A18" s="92" t="inlineStr">
+        <is>
+          <t>※ 소분류 12종을 하나씩 예시로 넣었습니다. 소분류를 고르면 행 전체 색이 자동으로 바뀝니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="92" t="inlineStr">
+        <is>
+          <t>※ 대표메뉴가 여러 개인 매장은 매장 정보를 그대로 반복해서 쓰고, 메뉴순번만 1·2·3으로 올려가며 행을 추가합니다. 매장번호가 같으면 같은 매장입니다. (1번 한식 3행, 5번 치킨 2행 참고 — 기울임꼴이 반복 입력 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="93" t="inlineStr">
+        <is>
+          <t>※ 상호명·주소·전화번호·평점은 형식을 보여주기 위한 가상의 값입니다. 실제 조사 값으로 바꿔서 쓰세요.</t>
         </is>
       </c>
     </row>
@@ -8248,355 +8904,355 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>서울대학교 시흥캠퍼스 인근 식당·카페 조사 템플릿</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="95" t="inlineStr">
         <is>
           <t>기본 규칙</t>
         </is>
       </c>
-      <c r="B3" s="45" t="n"/>
+      <c r="B3" s="96" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="97" t="inlineStr">
         <is>
           <t>1행 = 메뉴 1개</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="98" t="inlineStr">
         <is>
           <t>대표메뉴 1개가 1행입니다. 한 매장에 대표메뉴가 3개면 3행을 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="97" t="inlineStr">
         <is>
           <t>매장 정보 반복</t>
         </is>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="98" t="inlineStr">
         <is>
           <t>같은 매장의 2번째 이후 행에도 매장번호~최소주문금액을 똑같이 채웁니다. (빈칸 금지 — 정렬·필터 시 정보가 흩어집니다)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="97" t="inlineStr">
         <is>
           <t>매장번호</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>매장마다 1부터 부여하는 번호. 같은 매장의 모든 행에 같은 번호를 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="97" t="inlineStr">
         <is>
           <t>메뉴순번</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B7" s="98" t="inlineStr">
         <is>
           <t>그 매장 안에서의 대표메뉴 순서. 1, 2, 3 …</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="95" t="inlineStr">
         <is>
           <t>컬럼별 입력 규칙</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n"/>
+      <c r="B9" s="96" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="97" t="inlineStr">
         <is>
           <t>상호명(지점명 포함)</t>
         </is>
       </c>
-      <c r="B10" s="47" t="inlineStr">
+      <c r="B10" s="98" t="inlineStr">
         <is>
           <t>간판/지도 표기 그대로. 예) 교촌치킨 시흥배곧점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="97" t="inlineStr">
         <is>
           <t>대분류</t>
         </is>
       </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B11" s="98" t="inlineStr">
         <is>
           <t>드롭다운에서 식당 / 카페 중 선택.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="97" t="inlineStr">
         <is>
           <t>소분류</t>
         </is>
       </c>
-      <c r="B12" s="47" t="inlineStr">
+      <c r="B12" s="98" t="inlineStr">
         <is>
           <t>대분류를 먼저 고르면 해당 소분류만 드롭다운에 나옵니다. 선택하면 행 전체 색이 자동으로 바뀝니다.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="97" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B13" s="47" t="inlineStr">
+      <c r="B13" s="98" t="inlineStr">
         <is>
           <t>도로명 주소 기준. 층·호수까지 있으면 함께 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="97" t="inlineStr">
         <is>
           <t>운영시간</t>
         </is>
       </c>
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="98" t="inlineStr">
         <is>
           <t>예) 10:00~22:00 / 브레이크타임이나 요일별 차이가 있으면 괄호로 덧붙입니다.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="97" t="inlineStr">
         <is>
           <t>휴무일</t>
         </is>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B15" s="98" t="inlineStr">
         <is>
           <t>예) 매주 월요일, 연중무휴, 설·추석 당일</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="A16" s="97" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="B16" s="47" t="inlineStr">
+      <c r="B16" s="98" t="inlineStr">
         <is>
           <t>하이픈 포함 문자열로 저장됩니다. 예) 031-000-0000</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="A17" s="97" t="inlineStr">
         <is>
           <t>매장 평점</t>
         </is>
       </c>
-      <c r="B17" s="47" t="inlineStr">
+      <c r="B17" s="98" t="inlineStr">
         <is>
           <t>0.0 ~ 5.0. 배달앱·지도 중 어디서 봤는지 팀 내에서 기준을 통일하세요.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="97" t="inlineStr">
         <is>
           <t>예측 배달시간(분)</t>
         </is>
       </c>
-      <c r="B18" s="47" t="inlineStr">
+      <c r="B18" s="98" t="inlineStr">
         <is>
           <t>0 ~ 240 사이 정수. '30~40분'처럼 범위로 나오면 중앙값 또는 최댓값 등 기준을 통일합니다.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="A19" s="97" t="inlineStr">
         <is>
           <t>최소주문금액(원)</t>
         </is>
       </c>
-      <c r="B19" s="47" t="inlineStr">
+      <c r="B19" s="98" t="inlineStr">
         <is>
           <t>숫자만. 배달 최소주문금액이 없으면 0.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="97" t="inlineStr">
         <is>
           <t>대표메뉴 / 가격(원)</t>
         </is>
       </c>
-      <c r="B20" s="47" t="inlineStr">
+      <c r="B20" s="98" t="inlineStr">
         <is>
           <t>메뉴판 표기 그대로. 가격은 숫자만 (예: 23000).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="95" t="inlineStr">
         <is>
           <t>카테고리 색상표</t>
         </is>
       </c>
-      <c r="B22" s="45" t="n"/>
+      <c r="B22" s="96" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="99" t="inlineStr">
         <is>
           <t>식당 › 한식</t>
         </is>
       </c>
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="100" t="inlineStr">
         <is>
           <t>소분류에 '한식'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>식당 › 중식</t>
         </is>
       </c>
-      <c r="B24" s="49" t="inlineStr">
+      <c r="B24" s="100" t="inlineStr">
         <is>
           <t>소분류에 '중식'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="51" t="inlineStr">
+      <c r="A25" s="102" t="inlineStr">
         <is>
           <t>식당 › 일식</t>
         </is>
       </c>
-      <c r="B25" s="49" t="inlineStr">
+      <c r="B25" s="100" t="inlineStr">
         <is>
           <t>소분류에 '일식'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="52" t="inlineStr">
+      <c r="A26" s="103" t="inlineStr">
         <is>
           <t>식당 › 양식</t>
         </is>
       </c>
-      <c r="B26" s="49" t="inlineStr">
+      <c r="B26" s="100" t="inlineStr">
         <is>
           <t>소분류에 '양식'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="53" t="inlineStr">
+      <c r="A27" s="104" t="inlineStr">
         <is>
           <t>식당 › 치킨</t>
         </is>
       </c>
-      <c r="B27" s="49" t="inlineStr">
+      <c r="B27" s="100" t="inlineStr">
         <is>
           <t>소분류에 '치킨'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="54" t="inlineStr">
+      <c r="A28" s="105" t="inlineStr">
         <is>
           <t>식당 › 피자</t>
         </is>
       </c>
-      <c r="B28" s="49" t="inlineStr">
+      <c r="B28" s="100" t="inlineStr">
         <is>
           <t>소분류에 '피자'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="106" t="inlineStr">
         <is>
           <t>식당 › 족발</t>
         </is>
       </c>
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="100" t="inlineStr">
         <is>
           <t>소분류에 '족발'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="56" t="inlineStr">
+      <c r="A30" s="107" t="inlineStr">
         <is>
           <t>식당 › 보쌈</t>
         </is>
       </c>
-      <c r="B30" s="49" t="inlineStr">
+      <c r="B30" s="100" t="inlineStr">
         <is>
           <t>소분류에 '보쌈'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="57" t="inlineStr">
+      <c r="A31" s="108" t="inlineStr">
         <is>
           <t>식당 › 분식</t>
         </is>
       </c>
-      <c r="B31" s="49" t="inlineStr">
+      <c r="B31" s="100" t="inlineStr">
         <is>
           <t>소분류에 '분식'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="58" t="inlineStr">
+      <c r="A32" s="109" t="inlineStr">
         <is>
           <t>식당 › 패스트푸드</t>
         </is>
       </c>
-      <c r="B32" s="49" t="inlineStr">
+      <c r="B32" s="100" t="inlineStr">
         <is>
           <t>소분류에 '패스트푸드'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="59" t="inlineStr">
+      <c r="A33" s="110" t="inlineStr">
         <is>
           <t>카페 › 카페</t>
         </is>
       </c>
-      <c r="B33" s="49" t="inlineStr">
+      <c r="B33" s="100" t="inlineStr">
         <is>
           <t>소분류에 '카페'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="111" t="inlineStr">
         <is>
           <t>카페 › 디저트</t>
         </is>
       </c>
-      <c r="B34" s="49" t="inlineStr">
+      <c r="B34" s="100" t="inlineStr">
         <is>
           <t>소분류에 '디저트'를 입력하면 이 색으로 행 전체가 칠해집니다.</t>
         </is>
